--- a/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7FBFC47-D487-4CCF-A436-499D92421CB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0252FD81-39B1-4915-9CA8-185A5DCA8B18}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87096515-0913-4BEB-B414-53D1DF3E3DFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68036D2B-4FBE-4B52-8D09-35D6355A8FFE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95049B4-937E-4D6B-AD22-775F623B97E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27E9A03E-8B31-4442-85EE-50E1D67C64B1}"/>
 </file>